--- a/data/trans_orig/P36BPD10_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22671</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47719</t>
+          <t>46544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>24926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>43604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50760</t>
+          <t>52803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83013</t>
+          <t>84900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>182652</t>
+          <t>180271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228029</t>
+          <t>228303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152674</t>
+          <t>155675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>188846</t>
+          <t>189278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>347743</t>
+          <t>347578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>406260</t>
+          <t>405399</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>244529</t>
+          <t>241322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>291379</t>
+          <t>291409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>225314</t>
+          <t>224284</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>261321</t>
+          <t>260579</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>479936</t>
+          <t>481340</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>538522</t>
+          <t>537302</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36400</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>65355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24911</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44745</t>
+          <t>45184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66916</t>
+          <t>67812</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101362</t>
+          <t>102878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>190660</t>
+          <t>190635</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>234176</t>
+          <t>233373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143074</t>
+          <t>141311</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>174735</t>
+          <t>175450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340265</t>
+          <t>344641</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>397032</t>
+          <t>399734</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168095</t>
+          <t>169228</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209731</t>
+          <t>212687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>173546</t>
+          <t>172843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206209</t>
+          <t>208178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>353321</t>
+          <t>352440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409530</t>
+          <t>409512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>16335</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>83514</t>
+          <t>82870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92051</t>
+          <t>89602</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>290626</t>
+          <t>289720</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>575240</t>
+          <t>570877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60641</t>
+          <t>59910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81078</t>
+          <t>80093</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357881</t>
+          <t>359076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>691624</t>
+          <t>676351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>81,07%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74162</t>
+          <t>75701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298598</t>
+          <t>301054</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75059</t>
+          <t>75131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95575</t>
+          <t>95620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>117085</t>
+          <t>128134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391051</t>
+          <t>390165</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71871</t>
+          <t>72648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126782</t>
+          <t>126089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37055</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94819</t>
+          <t>92625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,47 +2148,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>160967</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>108280</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>195116</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,0%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>9,7%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>160967</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>111858</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>199551</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441538</t>
+          <t>445483</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>515769</t>
+          <t>515746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171197</t>
+          <t>172438</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>422191</t>
+          <t>418852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>577020</t>
+          <t>578241</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>909182</t>
+          <t>908354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>427825</t>
+          <t>427755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>500583</t>
+          <t>497000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>469945</t>
+          <t>471320</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>769517</t>
+          <t>763349</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>922616</t>
+          <t>923341</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1315211</t>
+          <t>1332725</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33009</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>59976</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>39807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68149</t>
+          <t>68342</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80711</t>
+          <t>81229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>119418</t>
+          <t>118549</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>241943</t>
+          <t>240152</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>285697</t>
+          <t>285386</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>384136</t>
+          <t>379660</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>542957</t>
+          <t>534143</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>642633</t>
+          <t>641521</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>804955</t>
+          <t>802757</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142051</t>
+          <t>140915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184454</t>
+          <t>184202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>261261</t>
+          <t>272910</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>404471</t>
+          <t>412379</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>432057</t>
+          <t>432292</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>573009</t>
+          <t>572364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64632</t>
+          <t>61864</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66365</t>
+          <t>65923</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>100183</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99219</t>
+          <t>96487</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>152606</t>
+          <t>151235</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>81206</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132937</t>
+          <t>135084</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>370413</t>
+          <t>368796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>423392</t>
+          <t>422213</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>467276</t>
+          <t>467760</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>544505</t>
+          <t>539957</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,93%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71101</t>
+          <t>66092</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121987</t>
+          <t>119220</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>258201</t>
+          <t>258545</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>309565</t>
+          <t>310540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338887</t>
+          <t>344096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>411669</t>
+          <t>418597</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,81%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>246111</t>
+          <t>240382</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>360393</t>
+          <t>360645</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>228305</t>
+          <t>228750</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>316564</t>
+          <t>319676</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>510172</t>
+          <t>513030</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>655315</t>
+          <t>659591</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1550035</t>
+          <t>1551045</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2092061</t>
+          <t>2168750</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1291933</t>
+          <t>1261369</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1696532</t>
+          <t>1691838</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3001970</t>
+          <t>2990668</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3702149</t>
+          <t>3727253</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1037603</t>
+          <t>998058</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1489342</t>
+          <t>1488755</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1585669</t>
+          <t>1593066</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2065818</t>
+          <t>2083051</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2765243</t>
+          <t>2755060</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3399040</t>
+          <t>3436554</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD10_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32980</t>
+          <t>36851</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>53664</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43604</t>
+          <t>53364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66677</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52803</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>95944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>205420</t>
+          <t>229645</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>180271</t>
+          <t>205595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228303</t>
+          <t>252146</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>171117</t>
+          <t>187371</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155675</t>
+          <t>168890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189278</t>
+          <t>207066</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>376537</t>
+          <t>417016</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>347578</t>
+          <t>388184</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>405399</t>
+          <t>446765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266812</t>
+          <t>284122</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>241322</t>
+          <t>261983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>291409</t>
+          <t>307525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>242654</t>
+          <t>260883</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>224284</t>
+          <t>241278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260579</t>
+          <t>280083</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>509465</t>
+          <t>545006</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>481340</t>
+          <t>515279</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>537302</t>
+          <t>574235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49545</t>
+          <t>52893</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65355</t>
+          <t>70349</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25138</t>
+          <t>28625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>83172</t>
+          <t>91813</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67812</t>
+          <t>74105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102878</t>
+          <t>112248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>213323</t>
+          <t>228572</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>190635</t>
+          <t>207181</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>233373</t>
+          <t>253752</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>158761</t>
+          <t>175962</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>141311</t>
+          <t>157900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>175450</t>
+          <t>192452</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>372083</t>
+          <t>404535</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>344641</t>
+          <t>376898</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>399734</t>
+          <t>433072</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>189345</t>
+          <t>201747</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169228</t>
+          <t>179104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212687</t>
+          <t>223470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>190192</t>
+          <t>208261</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172843</t>
+          <t>192016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208178</t>
+          <t>227090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>379538</t>
+          <t>410008</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352440</t>
+          <t>379093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409512</t>
+          <t>435769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48451</t>
+          <t>53942</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>39587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82870</t>
+          <t>69746</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>59601</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26445</t>
+          <t>52576</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89602</t>
+          <t>85986</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>434186</t>
+          <t>211113</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>289720</t>
+          <t>185547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>570877</t>
+          <t>231940</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70696</t>
+          <t>81058</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59910</t>
+          <t>70070</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80093</t>
+          <t>92425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>504882</t>
+          <t>292172</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359076</t>
+          <t>265785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>676351</t>
+          <t>318603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>184748</t>
+          <t>205691</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75701</t>
+          <t>183533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301054</t>
+          <t>230303</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>85065</t>
+          <t>92522</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75131</t>
+          <t>81071</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95620</t>
+          <t>104248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>269813</t>
+          <t>298213</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128134</t>
+          <t>273374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>390165</t>
+          <t>326723</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667385</t>
+          <t>470746</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667385</t>
+          <t>470746</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667385</t>
+          <t>470746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834296</t>
+          <t>658243</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834296</t>
+          <t>658243</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834296</t>
+          <t>658243</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>93241</t>
+          <t>97029</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72648</t>
+          <t>76960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126089</t>
+          <t>122814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31817</t>
+          <t>62468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92625</t>
+          <t>93515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>160967</t>
+          <t>174479</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108280</t>
+          <t>148847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195116</t>
+          <t>199513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>479221</t>
+          <t>533111</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>445483</t>
+          <t>498018</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>515746</t>
+          <t>573282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>324830</t>
+          <t>363333</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172438</t>
+          <t>339581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>418852</t>
+          <t>390023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>804052</t>
+          <t>896443</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>578241</t>
+          <t>854325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>908354</t>
+          <t>938381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>461759</t>
+          <t>501003</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>427755</t>
+          <t>462877</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>497000</t>
+          <t>533499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>585127</t>
+          <t>420012</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>471320</t>
+          <t>394648</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>763349</t>
+          <t>446348</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1046885</t>
+          <t>921015</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>923341</t>
+          <t>878488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1332725</t>
+          <t>963103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>48,35%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034221</t>
+          <t>1131143</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034221</t>
+          <t>1131143</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034221</t>
+          <t>1131143</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977683</t>
+          <t>860795</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977683</t>
+          <t>860795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977683</t>
+          <t>860795</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2011904</t>
+          <t>1991938</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2011904</t>
+          <t>1991938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2011904</t>
+          <t>1991938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>46142</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34611</t>
+          <t>44087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59976</t>
+          <t>73224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53980</t>
+          <t>62628</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39807</t>
+          <t>51279</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68342</t>
+          <t>76584</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100122</t>
+          <t>120131</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81229</t>
+          <t>100135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118549</t>
+          <t>139861</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>263300</t>
+          <t>313143</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240152</t>
+          <t>286491</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>285386</t>
+          <t>336716</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>438517</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>379660</t>
+          <t>397269</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>534143</t>
+          <t>446553</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>701816</t>
+          <t>732073</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>641521</t>
+          <t>693482</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>802757</t>
+          <t>766463</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>162909</t>
+          <t>194742</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>140915</t>
+          <t>170746</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184202</t>
+          <t>221482</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>348173</t>
+          <t>348535</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>272910</t>
+          <t>324268</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>412379</t>
+          <t>371549</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>511083</t>
+          <t>543277</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>432292</t>
+          <t>510559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>572364</t>
+          <t>580634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>472351</t>
+          <t>565388</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>472351</t>
+          <t>565388</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472351</t>
+          <t>565388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>840670</t>
+          <t>830093</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>840670</t>
+          <t>830093</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>840670</t>
+          <t>830093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1313021</t>
+          <t>1395481</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313021</t>
+          <t>1395481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1313021</t>
+          <t>1395481</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>39523</t>
+          <t>36142</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>20506</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61864</t>
+          <t>54873</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>81228</t>
+          <t>92664</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65923</t>
+          <t>75912</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>100183</t>
+          <t>112772</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>120751</t>
+          <t>128806</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>96487</t>
+          <t>103082</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>151235</t>
+          <t>155062</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>113291</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>84122</t>
+          <t>88452</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135084</t>
+          <t>138364</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>396390</t>
+          <t>445383</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>368796</t>
+          <t>417144</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>422213</t>
+          <t>472406</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>503477</t>
+          <t>558674</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>467760</t>
+          <t>520580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>539957</t>
+          <t>593266</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>93897</t>
+          <t>87795</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>66091</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>119220</t>
+          <t>115068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>283111</t>
+          <t>305543</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>258545</t>
+          <t>280916</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>310540</t>
+          <t>334322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>377008</t>
+          <t>393339</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>344096</t>
+          <t>359911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>418597</t>
+          <t>433666</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760729</t>
+          <t>843590</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001236</t>
+          <t>1080818</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001236</t>
+          <t>1080818</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001236</t>
+          <t>1080818</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>309883</t>
+          <t>334359</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>240382</t>
+          <t>299276</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>360645</t>
+          <t>384116</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>281408</t>
+          <t>325735</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>228750</t>
+          <t>296341</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>319676</t>
+          <t>359648</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>591290</t>
+          <t>660095</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>513030</t>
+          <t>609512</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>659591</t>
+          <t>713169</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1702538</t>
+          <t>1628875</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1551045</t>
+          <t>1564396</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2168750</t>
+          <t>1691005</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1560310</t>
+          <t>1672037</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1261369</t>
+          <t>1615510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1691838</t>
+          <t>1721922</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3262848</t>
+          <t>3300912</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2990668</t>
+          <t>3222658</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3727253</t>
+          <t>3386902</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1359470</t>
+          <t>1475100</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>998058</t>
+          <t>1412553</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1488755</t>
+          <t>1537061</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1734323</t>
+          <t>1635757</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1593066</t>
+          <t>1579423</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2083051</t>
+          <t>1686656</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3093792</t>
+          <t>3110857</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2755060</t>
+          <t>3021997</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3436554</t>
+          <t>3190761</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3371890</t>
+          <t>3438335</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3371890</t>
+          <t>3438335</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3371890</t>
+          <t>3438335</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3576040</t>
+          <t>3633529</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3576040</t>
+          <t>3633529</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3576040</t>
+          <t>3633529</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6947930</t>
+          <t>7071864</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6947930</t>
+          <t>7071864</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6947930</t>
+          <t>7071864</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
